--- a/farmer_forms/005_farmland_transition_feedback_form--farmer_forms.xlsx
+++ b/farmer_forms/005_farmland_transition_feedback_form--farmer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -923,12 +923,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>farm_equipment</t>
+          <t>farm_equipment_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Farm Equipment</t>
+          <t>Farm Equipment 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -969,12 +969,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -992,12 +992,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>submission_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submission Time</t>
+          <t>Submission Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>land_use</t>
+          <t>land_use_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Land Use</t>
+          <t>Land Use 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>prophets_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prophets</t>
+          <t>Prophets 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submission_user</t>
+          <t>submission_user_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Submission User</t>
+          <t>Submission User 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submission_device</t>
+          <t>submission_device_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submission Device</t>
+          <t>Submission Device 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1449,197 +1449,180 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>farming</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>prophets_choices</t>
+          <t>farm_equipment_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>farming</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>farm_equipment_choices</t>
+          <t>farm_equipment_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>farm_equipment_choices</t>
+          <t>land_use_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>land_use_choices</t>
+          <t>land_use_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>land_use_choices</t>
+          <t>prophets_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prophets_choices</t>
+          <t>prophets_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prophets_choices</t>
+          <t>submission_user_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>submission_user_choices</t>
+          <t>submission_user_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>submission_user_choices</t>
+          <t>submission_device_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>submission_device_choices</t>
+          <t>submission_device_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>submission_device_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
